--- a/docentes/Vargas Olvera Francisco Eduardo - Estadisticos 20241.xlsx
+++ b/docentes/Vargas Olvera Francisco Eduardo - Estadisticos 20241.xlsx
@@ -82,19 +82,19 @@
     <t>PERALTA</t>
   </si>
   <si>
-    <t>ACOSTA</t>
+    <t>TORRES</t>
   </si>
   <si>
     <t>TRONCO</t>
   </si>
   <si>
-    <t>CASTELLANOS</t>
+    <t>AJACTLE</t>
   </si>
   <si>
     <t>SANTIAGO ZURIEL</t>
   </si>
   <si>
-    <t>ELIZABETH</t>
+    <t>DAVID</t>
   </si>
 </sst>
 </file>
@@ -664,16 +664,19 @@
         <v>40</v>
       </c>
       <c r="D2">
-        <v>40</v>
+        <v>0</v>
       </c>
       <c r="E2">
-        <v>40</v>
+        <v>4</v>
       </c>
       <c r="F2">
-        <v>0</v>
+        <v>36</v>
       </c>
       <c r="G2">
-        <v>0</v>
+        <v>90</v>
+      </c>
+      <c r="H2">
+        <v>7.7</v>
       </c>
     </row>
     <row r="3" spans="1:8">
@@ -687,16 +690,19 @@
         <v>41</v>
       </c>
       <c r="D3">
-        <v>41</v>
+        <v>0</v>
       </c>
       <c r="E3">
-        <v>40</v>
+        <v>5</v>
       </c>
       <c r="F3">
-        <v>0</v>
+        <v>35</v>
       </c>
       <c r="G3">
-        <v>0</v>
+        <v>85.37</v>
+      </c>
+      <c r="H3">
+        <v>6.4</v>
       </c>
     </row>
     <row r="4" spans="1:8">
@@ -710,16 +716,19 @@
         <v>48</v>
       </c>
       <c r="D4">
-        <v>48</v>
+        <v>0</v>
       </c>
       <c r="E4">
-        <v>47</v>
+        <v>3</v>
       </c>
       <c r="F4">
-        <v>0</v>
+        <v>45</v>
       </c>
       <c r="G4">
-        <v>0</v>
+        <v>93.75</v>
+      </c>
+      <c r="H4">
+        <v>7.3</v>
       </c>
     </row>
     <row r="5" spans="1:8">
@@ -733,16 +742,19 @@
         <v>36</v>
       </c>
       <c r="D5">
-        <v>36</v>
+        <v>0</v>
       </c>
       <c r="E5">
-        <v>36</v>
+        <v>2</v>
       </c>
       <c r="F5">
-        <v>0</v>
+        <v>34</v>
       </c>
       <c r="G5">
-        <v>0</v>
+        <v>94.44</v>
+      </c>
+      <c r="H5">
+        <v>7.4</v>
       </c>
     </row>
     <row r="6" spans="1:8">
@@ -756,16 +768,19 @@
         <v>37</v>
       </c>
       <c r="D6">
-        <v>37</v>
+        <v>0</v>
       </c>
       <c r="E6">
-        <v>37</v>
+        <v>3</v>
       </c>
       <c r="F6">
-        <v>0</v>
+        <v>34</v>
       </c>
       <c r="G6">
-        <v>0</v>
+        <v>91.89</v>
+      </c>
+      <c r="H6">
+        <v>7.1</v>
       </c>
     </row>
   </sheetData>
@@ -821,16 +836,16 @@
         <v>0</v>
       </c>
       <c r="E2">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F2">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="G2">
-        <v>92.5</v>
+        <v>90</v>
       </c>
       <c r="H2">
-        <v>7.7</v>
+        <v>7.8</v>
       </c>
     </row>
     <row r="3" spans="1:8">
@@ -847,16 +862,16 @@
         <v>0</v>
       </c>
       <c r="E3">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="F3">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="G3">
-        <v>87.8</v>
+        <v>85.37</v>
       </c>
       <c r="H3">
-        <v>6.3</v>
+        <v>6.8</v>
       </c>
     </row>
     <row r="4" spans="1:8">
@@ -873,16 +888,16 @@
         <v>0</v>
       </c>
       <c r="E4">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="F4">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="G4">
-        <v>91.67</v>
+        <v>93.75</v>
       </c>
       <c r="H4">
-        <v>7.4</v>
+        <v>7.9</v>
       </c>
     </row>
     <row r="5" spans="1:8">
@@ -899,16 +914,16 @@
         <v>0</v>
       </c>
       <c r="E5">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F5">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="G5">
-        <v>100</v>
+        <v>94.44</v>
       </c>
       <c r="H5">
-        <v>7.3</v>
+        <v>7.5</v>
       </c>
     </row>
     <row r="6" spans="1:8">
@@ -934,7 +949,7 @@
         <v>91.89</v>
       </c>
       <c r="H6">
-        <v>7.1</v>
+        <v>7.5</v>
       </c>
     </row>
   </sheetData>
@@ -999,7 +1014,7 @@
     </row>
     <row r="3" spans="1:7">
       <c r="A3">
-        <v>24330051920114</v>
+        <v>24330051920299</v>
       </c>
       <c r="B3" t="s">
         <v>21</v>
@@ -1014,10 +1029,10 @@
         <v>8</v>
       </c>
       <c r="F3" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="G3">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
   </sheetData>

--- a/docentes/Vargas Olvera Francisco Eduardo - Estadisticos 20241.xlsx
+++ b/docentes/Vargas Olvera Francisco Eduardo - Estadisticos 20241.xlsx
@@ -1009,7 +1009,7 @@
         <v>10</v>
       </c>
       <c r="G2">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="3" spans="1:7">
@@ -1032,7 +1032,7 @@
         <v>10</v>
       </c>
       <c r="G3">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
   </sheetData>

--- a/docentes/Vargas Olvera Francisco Eduardo - Estadisticos 20241.xlsx
+++ b/docentes/Vargas Olvera Francisco Eduardo - Estadisticos 20241.xlsx
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="71" uniqueCount="26">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="81" uniqueCount="32">
   <si>
     <t>Mat</t>
   </si>
@@ -79,16 +79,34 @@
     <t>Reprobadas</t>
   </si>
   <si>
+    <t>CID</t>
+  </si>
+  <si>
+    <t>RAMOS</t>
+  </si>
+  <si>
     <t>PERALTA</t>
   </si>
   <si>
     <t>TORRES</t>
   </si>
   <si>
+    <t>OROZCO</t>
+  </si>
+  <si>
+    <t>CHICUELLAR</t>
+  </si>
+  <si>
     <t>TRONCO</t>
   </si>
   <si>
     <t>AJACTLE</t>
+  </si>
+  <si>
+    <t>ANGEL ALEXANDER</t>
+  </si>
+  <si>
+    <t>ELIAN RAMON</t>
   </si>
   <si>
     <t>SANTIAGO ZURIEL</t>
@@ -959,7 +977,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G3"/>
+  <dimension ref="A1:G5"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="4" width="15.7109375" customWidth="1"/>
@@ -991,39 +1009,39 @@
     </row>
     <row r="2" spans="1:7">
       <c r="A2">
-        <v>24330051920111</v>
+        <v>24330051920328</v>
       </c>
       <c r="B2" t="s">
         <v>20</v>
       </c>
       <c r="C2" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="D2" t="s">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="E2" t="s">
         <v>8</v>
       </c>
       <c r="F2" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="G2">
-        <v>1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="3" spans="1:7">
       <c r="A3">
-        <v>24330051920299</v>
+        <v>24330051920332</v>
       </c>
       <c r="B3" t="s">
         <v>21</v>
       </c>
       <c r="C3" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="D3" t="s">
-        <v>25</v>
+        <v>29</v>
       </c>
       <c r="E3" t="s">
         <v>8</v>
@@ -1032,6 +1050,52 @@
         <v>10</v>
       </c>
       <c r="G3">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="4" spans="1:7">
+      <c r="A4">
+        <v>24330051920111</v>
+      </c>
+      <c r="B4" t="s">
+        <v>22</v>
+      </c>
+      <c r="C4" t="s">
+        <v>26</v>
+      </c>
+      <c r="D4" t="s">
+        <v>30</v>
+      </c>
+      <c r="E4" t="s">
+        <v>8</v>
+      </c>
+      <c r="F4" t="s">
+        <v>10</v>
+      </c>
+      <c r="G4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7">
+      <c r="A5">
+        <v>24330051920299</v>
+      </c>
+      <c r="B5" t="s">
+        <v>23</v>
+      </c>
+      <c r="C5" t="s">
+        <v>27</v>
+      </c>
+      <c r="D5" t="s">
+        <v>31</v>
+      </c>
+      <c r="E5" t="s">
+        <v>8</v>
+      </c>
+      <c r="F5" t="s">
+        <v>10</v>
+      </c>
+      <c r="G5">
         <v>1</v>
       </c>
     </row>

--- a/docentes/Vargas Olvera Francisco Eduardo - Estadisticos 20241.xlsx
+++ b/docentes/Vargas Olvera Francisco Eduardo - Estadisticos 20241.xlsx
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="81" uniqueCount="32">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="106" uniqueCount="47">
   <si>
     <t>Mat</t>
   </si>
@@ -82,6 +82,21 @@
     <t>CID</t>
   </si>
   <si>
+    <t>GONZALEZ</t>
+  </si>
+  <si>
+    <t>TRUJILLO</t>
+  </si>
+  <si>
+    <t>VILLEGAS</t>
+  </si>
+  <si>
+    <t>REYES</t>
+  </si>
+  <si>
+    <t>RAZCON</t>
+  </si>
+  <si>
     <t>RAMOS</t>
   </si>
   <si>
@@ -94,6 +109,21 @@
     <t>OROZCO</t>
   </si>
   <si>
+    <t>RANGEL</t>
+  </si>
+  <si>
+    <t>FLORES</t>
+  </si>
+  <si>
+    <t>SOLIS</t>
+  </si>
+  <si>
+    <t>MORA</t>
+  </si>
+  <si>
+    <t>ROJAS</t>
+  </si>
+  <si>
     <t>CHICUELLAR</t>
   </si>
   <si>
@@ -104,6 +134,21 @@
   </si>
   <si>
     <t>ANGEL ALEXANDER</t>
+  </si>
+  <si>
+    <t>AXEL BENITO</t>
+  </si>
+  <si>
+    <t>VALERIA</t>
+  </si>
+  <si>
+    <t>NAARA SAFIR</t>
+  </si>
+  <si>
+    <t>ANGEL GAEL</t>
+  </si>
+  <si>
+    <t>JOSE ARTURO</t>
   </si>
   <si>
     <t>ELIAN RAMON</t>
@@ -977,7 +1022,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G5"/>
+  <dimension ref="A1:G10"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="4" width="15.7109375" customWidth="1"/>
@@ -1015,10 +1060,10 @@
         <v>20</v>
       </c>
       <c r="C2" t="s">
-        <v>24</v>
+        <v>29</v>
       </c>
       <c r="D2" t="s">
-        <v>28</v>
+        <v>38</v>
       </c>
       <c r="E2" t="s">
         <v>8</v>
@@ -1032,70 +1077,185 @@
     </row>
     <row r="3" spans="1:7">
       <c r="A3">
-        <v>24330051920332</v>
+        <v>24330051920329</v>
       </c>
       <c r="B3" t="s">
         <v>21</v>
       </c>
       <c r="C3" t="s">
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="D3" t="s">
-        <v>29</v>
+        <v>39</v>
       </c>
       <c r="E3" t="s">
         <v>8</v>
       </c>
       <c r="F3" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="G3">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="4" spans="1:7">
       <c r="A4">
-        <v>24330051920111</v>
+        <v>24330051920348</v>
       </c>
       <c r="B4" t="s">
         <v>22</v>
       </c>
       <c r="C4" t="s">
-        <v>26</v>
+        <v>31</v>
       </c>
       <c r="D4" t="s">
-        <v>30</v>
+        <v>40</v>
       </c>
       <c r="E4" t="s">
         <v>8</v>
       </c>
       <c r="F4" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="G4">
-        <v>1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="5" spans="1:7">
       <c r="A5">
-        <v>24330051920299</v>
+        <v>24330051920162</v>
       </c>
       <c r="B5" t="s">
         <v>23</v>
       </c>
       <c r="C5" t="s">
+        <v>32</v>
+      </c>
+      <c r="D5" t="s">
+        <v>41</v>
+      </c>
+      <c r="E5" t="s">
+        <v>8</v>
+      </c>
+      <c r="F5" t="s">
+        <v>12</v>
+      </c>
+      <c r="G5">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="6" spans="1:7">
+      <c r="A6">
+        <v>24330051920375</v>
+      </c>
+      <c r="B6" t="s">
+        <v>24</v>
+      </c>
+      <c r="C6" t="s">
+        <v>33</v>
+      </c>
+      <c r="D6" t="s">
+        <v>42</v>
+      </c>
+      <c r="E6" t="s">
+        <v>8</v>
+      </c>
+      <c r="F6" t="s">
+        <v>13</v>
+      </c>
+      <c r="G6">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="7" spans="1:7">
+      <c r="A7">
+        <v>24330051920307</v>
+      </c>
+      <c r="B7" t="s">
+        <v>25</v>
+      </c>
+      <c r="C7" t="s">
+        <v>34</v>
+      </c>
+      <c r="D7" t="s">
+        <v>43</v>
+      </c>
+      <c r="E7" t="s">
+        <v>8</v>
+      </c>
+      <c r="F7" t="s">
+        <v>9</v>
+      </c>
+      <c r="G7">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="8" spans="1:7">
+      <c r="A8">
+        <v>24330051920332</v>
+      </c>
+      <c r="B8" t="s">
+        <v>26</v>
+      </c>
+      <c r="C8" t="s">
+        <v>35</v>
+      </c>
+      <c r="D8" t="s">
+        <v>44</v>
+      </c>
+      <c r="E8" t="s">
+        <v>8</v>
+      </c>
+      <c r="F8" t="s">
+        <v>10</v>
+      </c>
+      <c r="G8">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="9" spans="1:7">
+      <c r="A9">
+        <v>24330051920111</v>
+      </c>
+      <c r="B9" t="s">
         <v>27</v>
       </c>
-      <c r="D5" t="s">
-        <v>31</v>
-      </c>
-      <c r="E5" t="s">
-        <v>8</v>
-      </c>
-      <c r="F5" t="s">
+      <c r="C9" t="s">
+        <v>36</v>
+      </c>
+      <c r="D9" t="s">
+        <v>45</v>
+      </c>
+      <c r="E9" t="s">
+        <v>8</v>
+      </c>
+      <c r="F9" t="s">
         <v>10</v>
       </c>
-      <c r="G5">
+      <c r="G9">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="10" spans="1:7">
+      <c r="A10">
+        <v>24330051920299</v>
+      </c>
+      <c r="B10" t="s">
+        <v>28</v>
+      </c>
+      <c r="C10" t="s">
+        <v>37</v>
+      </c>
+      <c r="D10" t="s">
+        <v>46</v>
+      </c>
+      <c r="E10" t="s">
+        <v>8</v>
+      </c>
+      <c r="F10" t="s">
+        <v>10</v>
+      </c>
+      <c r="G10">
         <v>1</v>
       </c>
     </row>

--- a/docentes/Vargas Olvera Francisco Eduardo - Estadisticos 20241.xlsx
+++ b/docentes/Vargas Olvera Francisco Eduardo - Estadisticos 20241.xlsx
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="106" uniqueCount="47">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="111" uniqueCount="50">
   <si>
     <t>Mat</t>
   </si>
@@ -79,24 +79,27 @@
     <t>Reprobadas</t>
   </si>
   <si>
+    <t>TRUJILLO</t>
+  </si>
+  <si>
+    <t>VILLEGAS</t>
+  </si>
+  <si>
+    <t>REYES</t>
+  </si>
+  <si>
     <t>CID</t>
   </si>
   <si>
-    <t>GONZALEZ</t>
-  </si>
-  <si>
-    <t>TRUJILLO</t>
-  </si>
-  <si>
-    <t>VILLEGAS</t>
-  </si>
-  <si>
-    <t>REYES</t>
-  </si>
-  <si>
     <t>RAZCON</t>
   </si>
   <si>
+    <t>BAEZ</t>
+  </si>
+  <si>
+    <t>PEREZ</t>
+  </si>
+  <si>
     <t>RAMOS</t>
   </si>
   <si>
@@ -106,24 +109,27 @@
     <t>TORRES</t>
   </si>
   <si>
+    <t>FLORES</t>
+  </si>
+  <si>
+    <t>SOLIS</t>
+  </si>
+  <si>
+    <t>MORA</t>
+  </si>
+  <si>
     <t>OROZCO</t>
   </si>
   <si>
-    <t>RANGEL</t>
-  </si>
-  <si>
-    <t>FLORES</t>
-  </si>
-  <si>
-    <t>SOLIS</t>
-  </si>
-  <si>
-    <t>MORA</t>
-  </si>
-  <si>
     <t>ROJAS</t>
   </si>
   <si>
+    <t>LOPEZ</t>
+  </si>
+  <si>
+    <t>MARTINEZ</t>
+  </si>
+  <si>
     <t>CHICUELLAR</t>
   </si>
   <si>
@@ -133,22 +139,25 @@
     <t>AJACTLE</t>
   </si>
   <si>
+    <t>VALERIA</t>
+  </si>
+  <si>
+    <t>NAARA SAFIR</t>
+  </si>
+  <si>
+    <t>ANGEL GAEL</t>
+  </si>
+  <si>
     <t>ANGEL ALEXANDER</t>
   </si>
   <si>
-    <t>AXEL BENITO</t>
-  </si>
-  <si>
-    <t>VALERIA</t>
-  </si>
-  <si>
-    <t>NAARA SAFIR</t>
-  </si>
-  <si>
-    <t>ANGEL GAEL</t>
-  </si>
-  <si>
     <t>JOSE ARTURO</t>
+  </si>
+  <si>
+    <t>ULISES EZEQUIEL</t>
+  </si>
+  <si>
+    <t>CAROLINA DEL CARMEN</t>
   </si>
   <si>
     <t>ELIAN RAMON</t>
@@ -1022,7 +1031,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G10"/>
+  <dimension ref="A1:G11"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="4" width="15.7109375" customWidth="1"/>
@@ -1054,22 +1063,22 @@
     </row>
     <row r="2" spans="1:7">
       <c r="A2">
-        <v>24330051920328</v>
+        <v>24330051920348</v>
       </c>
       <c r="B2" t="s">
         <v>20</v>
       </c>
       <c r="C2" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="D2" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="E2" t="s">
         <v>8</v>
       </c>
       <c r="F2" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="G2">
         <v>4</v>
@@ -1077,22 +1086,22 @@
     </row>
     <row r="3" spans="1:7">
       <c r="A3">
-        <v>24330051920329</v>
+        <v>24330051920162</v>
       </c>
       <c r="B3" t="s">
         <v>21</v>
       </c>
       <c r="C3" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="D3" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="E3" t="s">
         <v>8</v>
       </c>
       <c r="F3" t="s">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="G3">
         <v>4</v>
@@ -1100,22 +1109,22 @@
     </row>
     <row r="4" spans="1:7">
       <c r="A4">
-        <v>24330051920348</v>
+        <v>24330051920375</v>
       </c>
       <c r="B4" t="s">
         <v>22</v>
       </c>
       <c r="C4" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="D4" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="E4" t="s">
         <v>8</v>
       </c>
       <c r="F4" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="G4">
         <v>4</v>
@@ -1123,68 +1132,68 @@
     </row>
     <row r="5" spans="1:7">
       <c r="A5">
-        <v>24330051920162</v>
+        <v>24330051920328</v>
       </c>
       <c r="B5" t="s">
         <v>23</v>
       </c>
       <c r="C5" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="D5" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="E5" t="s">
         <v>8</v>
       </c>
       <c r="F5" t="s">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="G5">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="6" spans="1:7">
       <c r="A6">
-        <v>24330051920375</v>
+        <v>24330051920307</v>
       </c>
       <c r="B6" t="s">
         <v>24</v>
       </c>
       <c r="C6" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="D6" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="E6" t="s">
         <v>8</v>
       </c>
       <c r="F6" t="s">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="G6">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="7" spans="1:7">
       <c r="A7">
-        <v>24330051920307</v>
+        <v>24330051920169</v>
       </c>
       <c r="B7" t="s">
         <v>25</v>
       </c>
       <c r="C7" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="D7" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="E7" t="s">
         <v>8</v>
       </c>
       <c r="F7" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="G7">
         <v>3</v>
@@ -1192,39 +1201,39 @@
     </row>
     <row r="8" spans="1:7">
       <c r="A8">
-        <v>24330051920332</v>
+        <v>24330051920139</v>
       </c>
       <c r="B8" t="s">
         <v>26</v>
       </c>
       <c r="C8" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="D8" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="E8" t="s">
         <v>8</v>
       </c>
       <c r="F8" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="G8">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="9" spans="1:7">
       <c r="A9">
-        <v>24330051920111</v>
+        <v>24330051920332</v>
       </c>
       <c r="B9" t="s">
         <v>27</v>
       </c>
       <c r="C9" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="D9" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="E9" t="s">
         <v>8</v>
@@ -1233,21 +1242,21 @@
         <v>10</v>
       </c>
       <c r="G9">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="10" spans="1:7">
       <c r="A10">
-        <v>24330051920299</v>
+        <v>24330051920111</v>
       </c>
       <c r="B10" t="s">
         <v>28</v>
       </c>
       <c r="C10" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="D10" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="E10" t="s">
         <v>8</v>
@@ -1256,6 +1265,29 @@
         <v>10</v>
       </c>
       <c r="G10">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="11" spans="1:7">
+      <c r="A11">
+        <v>24330051920299</v>
+      </c>
+      <c r="B11" t="s">
+        <v>29</v>
+      </c>
+      <c r="C11" t="s">
+        <v>39</v>
+      </c>
+      <c r="D11" t="s">
+        <v>49</v>
+      </c>
+      <c r="E11" t="s">
+        <v>8</v>
+      </c>
+      <c r="F11" t="s">
+        <v>10</v>
+      </c>
+      <c r="G11">
         <v>1</v>
       </c>
     </row>

--- a/docentes/Vargas Olvera Francisco Eduardo - Estadisticos 20241.xlsx
+++ b/docentes/Vargas Olvera Francisco Eduardo - Estadisticos 20241.xlsx
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="111" uniqueCount="50">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="111" uniqueCount="49">
   <si>
     <t>Mat</t>
   </si>
@@ -79,94 +79,91 @@
     <t>Reprobadas</t>
   </si>
   <si>
+    <t>HUERTA</t>
+  </si>
+  <si>
     <t>TRUJILLO</t>
   </si>
   <si>
-    <t>VILLEGAS</t>
-  </si>
-  <si>
-    <t>REYES</t>
+    <t>GONZALEZ</t>
+  </si>
+  <si>
+    <t>BAEZ</t>
+  </si>
+  <si>
+    <t>PEREZ</t>
   </si>
   <si>
     <t>CID</t>
   </si>
   <si>
+    <t>GARCIA</t>
+  </si>
+  <si>
     <t>RAZCON</t>
   </si>
   <si>
-    <t>BAEZ</t>
-  </si>
-  <si>
-    <t>PEREZ</t>
-  </si>
-  <si>
     <t>RAMOS</t>
   </si>
   <si>
-    <t>PERALTA</t>
-  </si>
-  <si>
-    <t>TORRES</t>
+    <t>ESTEVEZ</t>
   </si>
   <si>
     <t>FLORES</t>
   </si>
   <si>
-    <t>SOLIS</t>
-  </si>
-  <si>
-    <t>MORA</t>
+    <t>RANGEL</t>
+  </si>
+  <si>
+    <t>LOPEZ</t>
+  </si>
+  <si>
+    <t>MARTINEZ</t>
   </si>
   <si>
     <t>OROZCO</t>
   </si>
   <si>
+    <t>SANCHEZ</t>
+  </si>
+  <si>
     <t>ROJAS</t>
   </si>
   <si>
-    <t>LOPEZ</t>
-  </si>
-  <si>
-    <t>MARTINEZ</t>
-  </si>
-  <si>
     <t>CHICUELLAR</t>
   </si>
   <si>
-    <t>TRONCO</t>
-  </si>
-  <si>
-    <t>AJACTLE</t>
+    <t>MARIN</t>
+  </si>
+  <si>
+    <t>YERIEL</t>
   </si>
   <si>
     <t>VALERIA</t>
   </si>
   <si>
-    <t>NAARA SAFIR</t>
-  </si>
-  <si>
-    <t>ANGEL GAEL</t>
+    <t>AXEL BENITO</t>
+  </si>
+  <si>
+    <t>ULISES EZEQUIEL</t>
+  </si>
+  <si>
+    <t>CAROLINA DEL CARMEN</t>
   </si>
   <si>
     <t>ANGEL ALEXANDER</t>
   </si>
   <si>
+    <t>JOY JARA</t>
+  </si>
+  <si>
     <t>JOSE ARTURO</t>
   </si>
   <si>
-    <t>ULISES EZEQUIEL</t>
-  </si>
-  <si>
-    <t>CAROLINA DEL CARMEN</t>
-  </si>
-  <si>
     <t>ELIAN RAMON</t>
   </si>
   <si>
-    <t>SANTIAGO ZURIEL</t>
-  </si>
-  <si>
-    <t>DAVID</t>
+    <t>ESTRELLA MONTSERRAT</t>
   </si>
 </sst>
 </file>
@@ -908,13 +905,13 @@
         <v>0</v>
       </c>
       <c r="E2">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="F2">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="G2">
-        <v>90</v>
+        <v>85</v>
       </c>
       <c r="H2">
         <v>7.8</v>
@@ -934,16 +931,16 @@
         <v>0</v>
       </c>
       <c r="E3">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="F3">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="G3">
-        <v>85.37</v>
+        <v>90.23999999999999</v>
       </c>
       <c r="H3">
-        <v>6.8</v>
+        <v>7.1</v>
       </c>
     </row>
     <row r="4" spans="1:8">
@@ -960,13 +957,13 @@
         <v>0</v>
       </c>
       <c r="E4">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F4">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="G4">
-        <v>93.75</v>
+        <v>91.67</v>
       </c>
       <c r="H4">
         <v>7.9</v>
@@ -986,16 +983,16 @@
         <v>0</v>
       </c>
       <c r="E5">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F5">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="G5">
-        <v>94.44</v>
+        <v>97.22</v>
       </c>
       <c r="H5">
-        <v>7.5</v>
+        <v>7.8</v>
       </c>
     </row>
     <row r="6" spans="1:8">
@@ -1012,16 +1009,16 @@
         <v>0</v>
       </c>
       <c r="E6">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="F6">
-        <v>34</v>
+        <v>37</v>
       </c>
       <c r="G6">
-        <v>91.89</v>
+        <v>100</v>
       </c>
       <c r="H6">
-        <v>7.5</v>
+        <v>7.7</v>
       </c>
     </row>
   </sheetData>
@@ -1063,22 +1060,22 @@
     </row>
     <row r="2" spans="1:7">
       <c r="A2">
-        <v>24330051920348</v>
+        <v>24330051920145</v>
       </c>
       <c r="B2" t="s">
         <v>20</v>
       </c>
       <c r="C2" t="s">
-        <v>30</v>
+        <v>22</v>
       </c>
       <c r="D2" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="E2" t="s">
         <v>8</v>
       </c>
       <c r="F2" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="G2">
         <v>4</v>
@@ -1086,177 +1083,177 @@
     </row>
     <row r="3" spans="1:7">
       <c r="A3">
-        <v>24330051920162</v>
+        <v>24330051920348</v>
       </c>
       <c r="B3" t="s">
         <v>21</v>
       </c>
       <c r="C3" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="D3" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="E3" t="s">
         <v>8</v>
       </c>
       <c r="F3" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="G3">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="4" spans="1:7">
       <c r="A4">
-        <v>24330051920375</v>
+        <v>24330051920329</v>
       </c>
       <c r="B4" t="s">
         <v>22</v>
       </c>
       <c r="C4" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="D4" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="E4" t="s">
         <v>8</v>
       </c>
       <c r="F4" t="s">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="G4">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="5" spans="1:7">
       <c r="A5">
-        <v>24330051920328</v>
+        <v>24330051920169</v>
       </c>
       <c r="B5" t="s">
         <v>23</v>
       </c>
       <c r="C5" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="D5" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="E5" t="s">
         <v>8</v>
       </c>
       <c r="F5" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="G5">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="6" spans="1:7">
       <c r="A6">
-        <v>24330051920307</v>
+        <v>24330051920139</v>
       </c>
       <c r="B6" t="s">
         <v>24</v>
       </c>
       <c r="C6" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="D6" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="E6" t="s">
         <v>8</v>
       </c>
       <c r="F6" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="G6">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="7" spans="1:7">
       <c r="A7">
-        <v>24330051920169</v>
+        <v>24330051920328</v>
       </c>
       <c r="B7" t="s">
         <v>25</v>
       </c>
       <c r="C7" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="D7" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="E7" t="s">
         <v>8</v>
       </c>
       <c r="F7" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="G7">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="8" spans="1:7">
       <c r="A8">
-        <v>24330051920139</v>
+        <v>24330051920353</v>
       </c>
       <c r="B8" t="s">
         <v>26</v>
       </c>
       <c r="C8" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="D8" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="E8" t="s">
         <v>8</v>
       </c>
       <c r="F8" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="G8">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="9" spans="1:7">
       <c r="A9">
-        <v>24330051920332</v>
+        <v>24330051920307</v>
       </c>
       <c r="B9" t="s">
         <v>27</v>
       </c>
       <c r="C9" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="D9" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="E9" t="s">
         <v>8</v>
       </c>
       <c r="F9" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="G9">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="10" spans="1:7">
       <c r="A10">
-        <v>24330051920111</v>
+        <v>24330051920332</v>
       </c>
       <c r="B10" t="s">
         <v>28</v>
       </c>
       <c r="C10" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="D10" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="E10" t="s">
         <v>8</v>
@@ -1270,22 +1267,22 @@
     </row>
     <row r="11" spans="1:7">
       <c r="A11">
-        <v>24330051920299</v>
+        <v>24330051920250</v>
       </c>
       <c r="B11" t="s">
         <v>29</v>
       </c>
       <c r="C11" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="D11" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="E11" t="s">
         <v>8</v>
       </c>
       <c r="F11" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="G11">
         <v>1</v>
